--- a/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
@@ -1,43 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_Evidence" sheetId="1" r:id="R267dc424766e4dba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_INDEX" sheetId="2" r:id="R3e38dd470b4546ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="3" r:id="Ra7478d373ae94658"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_入力フロー" sheetId="4" r:id="Re92a65ad4ca947df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_取替方式" sheetId="5" r:id="R640bab79e42444b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_仕様区分" sheetId="6" r:id="R6402b05714814370"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_窓種" sheetId="7" r:id="Rd738667e50304da2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03A_枠仕様" sheetId="8" r:id="Rcfddc6c0404e41e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03B_窓種枠設定" sheetId="9" r:id="R5385cd98098b494c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_窓種固有仕様" sheetId="10" r:id="R9fa7463245354b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_サイズルール" sheetId="11" r:id="Rd40c607777c1467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_サイズ区間" sheetId="12" r:id="R1b19dc80e1ef442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05B_境界ルール" sheetId="13" r:id="Rbe6e4e9f1cf94acd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_色" sheetId="14" r:id="Rba77df2484cd4216"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06A_色適用条件" sheetId="15" r:id="R3932ba62a96f4f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_網戸" sheetId="16" r:id="R021b5c5e33ec4ca6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07A_網戸適用条件" sheetId="17" r:id="R4e98f3c7d13f499b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_ガラス" sheetId="18" r:id="Rbffed13c36ed449e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08A_ガラス適用条件" sheetId="19" r:id="Rf9d037d7eb4043c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_その他OP" sheetId="20" r:id="R77f2a0748fd94f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09A_OP依存関係" sheetId="21" r:id="Rc73d05e4926f47ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_適用条件" sheetId="22" r:id="Raecb361046ad4f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10A_既設窓互換" sheetId="23" r:id="R57626b3d366740c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10B_現調項目" sheetId="24" r:id="R38293e761e644d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_QA" sheetId="25" r:id="R1acaa5e2cc3f4c63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_開口構成" sheetId="26" r:id="R9b19cd5534774c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_見積入力テスト" sheetId="27" r:id="Re69569a30d884ba3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C_化粧カバー見付" sheetId="28" r:id="Rfd73b6859ade4c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02B_参照商品" sheetId="29" r:id="R73a5363f84e44017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02C_新設サッシ手配方式" sheetId="30" r:id="R88e22b8da493439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03C_対応TW窓種" sheetId="31" r:id="R186d7639cc05442f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03D_TW参照制限" sheetId="32" r:id="R11dc7809c3054af8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05C_寸法変換" sheetId="33" r:id="R627c3e5a31634823"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_共通参照" sheetId="34" r:id="Ra495668d44984d48"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="90_Evidence" sheetId="1" r:id="R267dc424766e4dba"/>
+    <sheet name="00_INDEX" sheetId="2" r:id="R3e38dd470b4546ed"/>
+    <sheet name="00_README" sheetId="3" r:id="Ra7478d373ae94658"/>
+    <sheet name="01_入力フロー" sheetId="4" r:id="Re92a65ad4ca947df"/>
+    <sheet name="02_取替方式" sheetId="5" r:id="R640bab79e42444b1"/>
+    <sheet name="02A_仕様区分" sheetId="6" r:id="R6402b05714814370"/>
+    <sheet name="03_窓種" sheetId="7" r:id="Rd738667e50304da2"/>
+    <sheet name="03A_枠仕様" sheetId="8" r:id="Rcfddc6c0404e41e3"/>
+    <sheet name="03B_窓種枠設定" sheetId="9" r:id="R5385cd98098b494c"/>
+    <sheet name="04_窓種固有仕様" sheetId="10" r:id="R9fa7463245354b06"/>
+    <sheet name="05_サイズルール" sheetId="11" r:id="Rd40c607777c1467d"/>
+    <sheet name="05A_サイズ区間" sheetId="12" r:id="R1b19dc80e1ef442d"/>
+    <sheet name="05B_境界ルール" sheetId="13" r:id="Rbe6e4e9f1cf94acd"/>
+    <sheet name="06_色" sheetId="14" r:id="Rba77df2484cd4216"/>
+    <sheet name="06A_色適用条件" sheetId="15" r:id="R3932ba62a96f4f65"/>
+    <sheet name="07_網戸" sheetId="16" r:id="R021b5c5e33ec4ca6"/>
+    <sheet name="07A_網戸適用条件" sheetId="17" r:id="R4e98f3c7d13f499b"/>
+    <sheet name="08_ガラス" sheetId="18" r:id="Rbffed13c36ed449e"/>
+    <sheet name="08A_ガラス適用条件" sheetId="19" r:id="Rf9d037d7eb4043c3"/>
+    <sheet name="09_その他OP" sheetId="20" r:id="R77f2a0748fd94f24"/>
+    <sheet name="09A_OP依存関係" sheetId="21" r:id="Rc73d05e4926f47ac"/>
+    <sheet name="10_適用条件" sheetId="22" r:id="Raecb361046ad4f82"/>
+    <sheet name="10A_既設窓互換" sheetId="23" r:id="R57626b3d366740c2"/>
+    <sheet name="10B_現調項目" sheetId="24" r:id="R38293e761e644d25"/>
+    <sheet name="99_QA" sheetId="25" r:id="R1acaa5e2cc3f4c63"/>
+    <sheet name="04A_開口構成" sheetId="26" r:id="R9b19cd5534774c34"/>
+    <sheet name="11_見積入力テスト" sheetId="27" r:id="Re69569a30d884ba3"/>
+    <sheet name="10C_化粧カバー見付" sheetId="28" r:id="Rfd73b6859ade4c14"/>
+    <sheet name="02B_参照商品" sheetId="29" r:id="R73a5363f84e44017"/>
+    <sheet name="02C_新設サッシ手配方式" sheetId="30" r:id="R88e22b8da493439c"/>
+    <sheet name="03C_対応TW窓種" sheetId="31" r:id="R186d7639cc05442f"/>
+    <sheet name="03D_TW参照制限" sheetId="32" r:id="R11dc7809c3054af8"/>
+    <sheet name="05C_寸法変換" sheetId="33" r:id="R627c3e5a31634823"/>
+    <sheet name="12_共通参照" sheetId="34" r:id="Ra495668d44984d48"/>
+    <sheet name="14_UI選択契約" sheetId="35" r:id="rIdReplusUiV9"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1213,6 +1214,383 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/replus-ui-v9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="184">
+        <v>リプラス住宅用・共通UI選択契約</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="186"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="str" s="181">
+        <v>分類</v>
+      </c>
+      <c r="B2" t="str" s="182">
+        <v>対象</v>
+      </c>
+      <c r="C2" t="str" s="182">
+        <v>依存元</v>
+      </c>
+      <c r="D2" t="str" s="182">
+        <v>処理</v>
+      </c>
+      <c r="E2" t="str" s="183">
+        <v>根拠区分</v>
+      </c>
+      <c r="F2" t="str">
+        <v>revision</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str" s="184">
+        <v>色連動</v>
+      </c>
+      <c r="B3" t="str" s="185">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C3" t="str" s="185">
+        <v>new_sash_exterior_color</v>
+      </c>
+      <c r="D3" t="str" s="185">
+        <v>{"targetField": "exterior_cover_color", "parents": ["new_sash_exterior_color"], "cases": [{"when": {"new_sash_exterior_color": "BLACK"}, "value": "T"}, {"when": {"new_sash_exterior_color": "T"}, "value": "T"}, {"when": {"new_sash_exterior_color": "EXT-T"}, "value": "T"}, {"when": {"new_sash_exterior_color": "EXT-LIX-T"}, "value": "T"}, {"when": {"new_sash_exterior_color": "AUTUMN_BROWN"}, "value": "G"}, {"when": {"new_sash_exterior_color": "G"}, "value": "G"}, {"when": {"new_sash_exterior_color": "EXT-G"}, "value": "G"}, {"when": {"new_sash_exterior_color": "EXT-LIX-G"}, "value": "G"}, {"when": {"new_sash_exterior_color": "SHINE_GRAY"}, "value": "K"}, {"when": {"new_sash_exterior_color": "K"}, "value": "K"}, {"when": {"new_sash_exterior_color": "EXT-K"}, "value": "K"}, {"when": {"new_sash_exterior_color": "EXT-LIX-K"}, "value": "K"}, {"when": {"new_sash_exterior_color": "NATURAL_SILVER"}, "value": "D"}, {"when": {"new_sash_exterior_color": "D"}, "value": "D"}, {"when": {"new_sash_exterior_color": "EXT-D"}, "value": "D"}, {"when": {"new_sash_exterior_color": "EXT-LIX-D"}, "value": "D"}, {"when": {"new_sash_exterior_color": "WHITE"}, "value": "W"}, {"when": {"new_sash_exterior_color": "W"}, "value": "W"}, {"when": {"new_sash_exterior_color": "EXT-W"}, "value": "W"}, {"when": {"new_sash_exterior_color": "EXT-LIX-W"}, "value": "W"}], "resolvedMessage": "本体外観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E3" t="str" s="186">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F3" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str" s="184">
+        <v>色連動</v>
+      </c>
+      <c r="B4" t="str" s="185">
+        <v>interior_cover_color</v>
+      </c>
+      <c r="C4" t="str" s="185">
+        <v>new_sash_interior_color</v>
+      </c>
+      <c r="D4" t="str" s="185">
+        <v>{"targetField": "interior_cover_color", "parents": ["new_sash_interior_color"], "cases": [{"when": {"new_sash_interior_color": "BLACK"}, "value": "M"}, {"when": {"new_sash_interior_color": "M"}, "value": "M"}, {"when": {"new_sash_interior_color": "INT-M"}, "value": "M"}, {"when": {"new_sash_interior_color": "INT-LIX-M"}, "value": "M"}, {"when": {"new_sash_interior_color": "CREA_MOCHA"}, "value": "C"}, {"when": {"new_sash_interior_color": "C"}, "value": "C"}, {"when": {"new_sash_interior_color": "INT-C"}, "value": "C"}, {"when": {"new_sash_interior_color": "INT-LIX-C"}, "value": "C"}, {"when": {"new_sash_interior_color": "CREA_RUSK"}, "value": "B"}, {"when": {"new_sash_interior_color": "B"}, "value": "B"}, {"when": {"new_sash_interior_color": "INT-B"}, "value": "B"}, {"when": {"new_sash_interior_color": "INT-LIX-B"}, "value": "B"}, {"when": {"new_sash_interior_color": "CREA_PALE"}, "value": "P"}, {"when": {"new_sash_interior_color": "P"}, "value": "P"}, {"when": {"new_sash_interior_color": "INT-P"}, "value": "P"}, {"when": {"new_sash_interior_color": "INT-LIX-P"}, "value": "P"}, {"when": {"new_sash_interior_color": "PRECIOUS_WHITE"}, "value": "F"}, {"when": {"new_sash_interior_color": "F"}, "value": "F"}, {"when": {"new_sash_interior_color": "INT-F"}, "value": "F"}, {"when": {"new_sash_interior_color": "INT-LIX-F"}, "value": "F"}], "resolvedMessage": "本体内観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E4" t="str" s="186">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F4" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B5" t="str" s="185">
+        <v>referenced_series_id</v>
+      </c>
+      <c r="C5" t="str" s="185"/>
+      <c r="D5" t="str" s="185">
+        <v>{"label": "新設サッシシリーズ", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E5" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F5" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B6" t="str" s="185">
+        <v>referenced_window_id</v>
+      </c>
+      <c r="C6" t="str" s="185">
+        <v>referenced_series_id</v>
+      </c>
+      <c r="D6" t="str" s="185">
+        <v>{"label": "新設サッシ窓種", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E6" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F6" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B7" t="str" s="185">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C7" t="str" s="185">
+        <v>new_sash_exterior_color</v>
+      </c>
+      <c r="D7" t="str" s="185">
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E7" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F7" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B8" t="str" s="185">
+        <v>interior_cover_color</v>
+      </c>
+      <c r="C8" t="str" s="185">
+        <v>new_sash_interior_color</v>
+      </c>
+      <c r="D8" t="str" s="185">
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E8" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F8" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B9" t="str" s="185">
+        <v>wooden_casing_color</v>
+      </c>
+      <c r="C9" t="str" s="185">
+        <v>options</v>
+      </c>
+      <c r="D9" t="str" s="185">
+        <v>{"label": "木製ケーシング色", "group": "part_detail", "internal": false}</v>
+      </c>
+      <c r="E9" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F9" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B10" t="str" s="185">
+        <v>options</v>
+      </c>
+      <c r="C10" t="str" s="185"/>
+      <c r="D10" t="str" s="185">
+        <v>{"label": "追加部材・オプション", "group": "options", "internal": false}</v>
+      </c>
+      <c r="E10" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F10" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B11" t="str" s="185">
+        <v>building_structure</v>
+      </c>
+      <c r="C11" t="str" s="185"/>
+      <c r="D11" t="str" s="185">
+        <v>{"label": "建物構造", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E11" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F11" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B12" t="str" s="185">
+        <v>survey_w</v>
+      </c>
+      <c r="C12" t="str" s="185"/>
+      <c r="D12" t="str" s="185">
+        <v>{"label": "採寸幅 WS（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E12" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F12" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B13" t="str" s="185">
+        <v>survey_h</v>
+      </c>
+      <c r="C13" t="str" s="185"/>
+      <c r="D13" t="str" s="185">
+        <v>{"label": "採寸高さ HS（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E13" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F13" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B14" t="str" s="185">
+        <v>lower_frame_rise</v>
+      </c>
+      <c r="C14" t="str" s="185"/>
+      <c r="D14" t="str" s="185">
+        <v>{"label": "既設下枠の立上り（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E14" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F14" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B15" t="str" s="185">
+        <v>existing_frame_depth</v>
+      </c>
+      <c r="C15" t="str" s="185"/>
+      <c r="D15" t="str" s="185">
+        <v>{"label": "既設枠見込み（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E15" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F15" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B16" t="str" s="185">
+        <v>interior_cover_type</v>
+      </c>
+      <c r="C16" t="str" s="185"/>
+      <c r="D16" t="str" s="185">
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E16" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F16" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B17" t="str" s="185">
+        <v>exterior_cover_type</v>
+      </c>
+      <c r="C17" t="str" s="185">
+        <v>survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+      </c>
+      <c r="D17" t="str" s="185">
+        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E17" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F17" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B18" t="str" s="185">
+        <v>survey_cover_top</v>
+      </c>
+      <c r="C18" t="str" s="185"/>
+      <c r="D18" t="str" s="185">
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E18" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F18" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B19" t="str" s="185">
+        <v>survey_cover_bottom</v>
+      </c>
+      <c r="C19" t="str" s="185"/>
+      <c r="D19" t="str" s="185">
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E19" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F19" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B20" t="str" s="185">
+        <v>survey_cover_side</v>
+      </c>
+      <c r="C20" t="str" s="185"/>
+      <c r="D20" t="str" s="185">
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E20" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F20" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9645,303 +10023,356 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="56" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="74" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="178" t="str">
-        <x:v>01_入力フロー｜アタッチ枠（TW用）</x:v>
-      </x:c>
-      <x:c r="B1" s="178"/>
-      <x:c r="C1" s="178"/>
-      <x:c r="D1" s="178"/>
-      <x:c r="E1" s="178"/>
-    </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="181" t="str">
-        <x:v>順序</x:v>
-      </x:c>
-      <x:c r="B3" s="182" t="str">
-        <x:v>表示項目</x:v>
-      </x:c>
-      <x:c r="C3" s="182" t="str">
-        <x:v>データキー</x:v>
-      </x:c>
-      <x:c r="D3" s="182" t="str">
-        <x:v>候補/入力</x:v>
-      </x:c>
-      <x:c r="E3" s="183" t="str">
-        <x:v>制御</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="184" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="185" t="str">
-        <x:v>取替方式</x:v>
-      </x:c>
-      <x:c r="C4" s="185" t="str">
-        <x:v>installation_system_id</x:v>
-      </x:c>
-      <x:c r="D4" s="185" t="str">
-        <x:v>RPL_ATT_TW</x:v>
-      </x:c>
-      <x:c r="E4" s="186" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="184" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="185" t="str">
-        <x:v>既設窓条件</x:v>
-      </x:c>
-      <x:c r="C5" s="185" t="str">
-        <x:v>existing_window_compatibility</x:v>
-      </x:c>
-      <x:c r="D5" s="185" t="str">
-        <x:v>既設窓種・材質・構造</x:v>
-      </x:c>
-      <x:c r="E5" s="186" t="str">
-        <x:v>現調レイヤーで先行判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="184" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="185" t="str">
-        <x:v>新設サッシ手配方式</x:v>
-      </x:c>
-      <x:c r="C6" s="185" t="str">
-        <x:v>new_sash_supply_mode</x:v>
-      </x:c>
-      <x:c r="D6" s="185" t="str">
-        <x:v>ATTACH_DEDICATED / TW_SEPARATE</x:v>
-      </x:c>
-      <x:c r="E6" s="186" t="str">
-        <x:v>対応窓種により候補表示</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="184" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="185" t="str">
-        <x:v>TW窓種</x:v>
-      </x:c>
-      <x:c r="C7" s="185" t="str">
-        <x:v>referenced_window_id</x:v>
-      </x:c>
-      <x:c r="D7" s="185" t="str">
-        <x:v>TW正本SWT ID</x:v>
-      </x:c>
-      <x:c r="E7" s="186" t="str">
-        <x:v>03C対応表で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="184" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="185" t="str">
-        <x:v>施工方法</x:v>
-      </x:c>
-      <x:c r="C8" s="185" t="str">
-        <x:v>installation_method</x:v>
-      </x:c>
-      <x:c r="D8" s="185" t="str">
-        <x:v>STANDARD / INNER_FIT_EXISTING_SINGLE</x:v>
-      </x:c>
-      <x:c r="E8" s="186" t="str">
-        <x:v>既設状態から決定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="184" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B9" s="185" t="str">
-        <x:v>採寸W/H</x:v>
-      </x:c>
-      <x:c r="C9" s="185" t="str">
-        <x:v>survey_w / survey_h</x:v>
-      </x:c>
-      <x:c r="D9" s="185" t="str">
-        <x:v>3点採寸の最小値</x:v>
-      </x:c>
-      <x:c r="E9" s="186" t="str">
-        <x:v>現調入力</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="184" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="185" t="str">
-        <x:v>アタッチ枠出来寸</x:v>
-      </x:c>
-      <x:c r="C10" s="185" t="str">
-        <x:v>attachment_finished_w/h</x:v>
-      </x:c>
-      <x:c r="D10" s="185" t="str">
-        <x:v>自動</x:v>
-      </x:c>
-      <x:c r="E10" s="186" t="str">
-        <x:v>WS/HS-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="184" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="185" t="str">
-        <x:v>TW製作寸法</x:v>
-      </x:c>
-      <x:c r="C11" s="185" t="str">
-        <x:v>referenced_product_w/h</x:v>
-      </x:c>
-      <x:c r="D11" s="185" t="str">
-        <x:v>自動</x:v>
-      </x:c>
-      <x:c r="E11" s="186" t="str">
-        <x:v>W=WS-38 / H=HS-50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="184" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" s="185" t="str">
-        <x:v>TW製作可否</x:v>
-      </x:c>
-      <x:c r="C12" s="185" t="str">
-        <x:v>referenced_size_validation</x:v>
-      </x:c>
-      <x:c r="D12" s="185" t="str">
-        <x:v>TW正本へ照会</x:v>
-      </x:c>
-      <x:c r="E12" s="186" t="str">
-        <x:v>TW正本のサイズルールを実行</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="184" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B13" s="185" t="str">
-        <x:v>アタッチ枠現調条件</x:v>
-      </x:c>
-      <x:c r="C13" s="185" t="str">
-        <x:v>attachment_validation</x:v>
-      </x:c>
-      <x:c r="D13" s="185" t="str">
-        <x:v>見込み/下枠/変形等</x:v>
-      </x:c>
-      <x:c r="E13" s="186" t="str">
-        <x:v>ローカルルールを実行</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="184" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" s="185" t="str">
-        <x:v>TW本体仕様</x:v>
-      </x:c>
-      <x:c r="C14" s="185" t="str">
-        <x:v>referenced_product_options</x:v>
-      </x:c>
-      <x:c r="D14" s="185" t="str">
-        <x:v>色・網戸・ガラス・本体OP</x:v>
-      </x:c>
-      <x:c r="E14" s="186" t="str">
-        <x:v>TW正本から取得</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="184" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" s="185" t="str">
-        <x:v>化粧カバー</x:v>
-      </x:c>
-      <x:c r="C15" s="185" t="str">
-        <x:v>exterior_cover_type/color</x:v>
-      </x:c>
-      <x:c r="D15" s="185" t="str">
-        <x:v>大/中/小＋5色</x:v>
-      </x:c>
-      <x:c r="E15" s="186" t="str">
-        <x:v>既設見付で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="184" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B16" s="185" t="str">
-        <x:v>室内部材</x:v>
-      </x:c>
-      <x:c r="C16" s="185" t="str">
-        <x:v>interior_cover</x:v>
-      </x:c>
-      <x:c r="D16" s="185" t="str">
-        <x:v>アングルカバー/見切材</x:v>
-      </x:c>
-      <x:c r="E16" s="186" t="str">
-        <x:v>アタッチ枠部材</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="184" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B17" s="185" t="str">
-        <x:v>リプラス側OP</x:v>
-      </x:c>
-      <x:c r="C17" s="185" t="str">
-        <x:v>attachment_option</x:v>
-      </x:c>
-      <x:c r="D17" s="185" t="str">
-        <x:v>施工部材等</x:v>
-      </x:c>
-      <x:c r="E17" s="186" t="str">
-        <x:v>09A依存を適用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="187" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B18" s="188" t="str">
-        <x:v>最終判定</x:v>
-      </x:c>
-      <x:c r="C18" s="188" t="str">
-        <x:v>final_eligibility</x:v>
-      </x:c>
-      <x:c r="D18" s="188" t="str">
-        <x:v>AUTO / EXTERNAL_CHECK</x:v>
-      </x:c>
-      <x:c r="E18" s="189" t="str">
-        <x:v>TW判定 AND アタッチ判定</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="56" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="74" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" t="str" s="178">
+        <v>リプラス住宅用・グローバルセレクションフロー</v>
+      </c>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" t="str" s="181">
+        <v>順番</v>
+      </c>
+      <c r="B3" t="str" s="182">
+        <v>表示項目</v>
+      </c>
+      <c r="C3" t="str" s="182">
+        <v>データキー</v>
+      </c>
+      <c r="D3" t="str" s="182">
+        <v>候補/入力</v>
+      </c>
+      <c r="E3" t="str" s="183">
+        <v>制御方針</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="184">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str" s="185">
+        <v>商品・リプラス仕様</v>
+      </c>
+      <c r="C4" t="str" s="185">
+        <v>product / specification</v>
+      </c>
+      <c r="D4" t="str" s="185">
+        <v>リプラス住宅用 → 仕様</v>
+      </c>
+      <c r="E4" t="str" s="186">
+        <v>今回承認されたアプリ運用ルール</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="184">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str" s="185">
+        <v>設置・施工条件</v>
+      </c>
+      <c r="C5" t="str" s="185">
+        <v>context</v>
+      </c>
+      <c r="D5" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E5" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="184">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str" s="185">
+        <v>窓種・基本仕様</v>
+      </c>
+      <c r="C6" t="str" s="185">
+        <v>opening</v>
+      </c>
+      <c r="D6" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E6" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="184">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str" s="185">
+        <v>本体色</v>
+      </c>
+      <c r="C7" t="str" s="185">
+        <v>finish</v>
+      </c>
+      <c r="D7" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E7" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="184">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str" s="185">
+        <v>網戸</v>
+      </c>
+      <c r="C8" t="str" s="185">
+        <v>screen</v>
+      </c>
+      <c r="D8" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E8" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="184">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str" s="185">
+        <v>ガラス</v>
+      </c>
+      <c r="C9" t="str" s="185">
+        <v>glazing</v>
+      </c>
+      <c r="D9" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E9" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="184">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str" s="185">
+        <v>室内側の仕上げ・アングルカバー</v>
+      </c>
+      <c r="C10" t="str" s="185">
+        <v>interior_finish</v>
+      </c>
+      <c r="D10" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E10" t="str" s="186">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="184">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str" s="185">
+        <v>室外側の仕上げ・化粧カバー</v>
+      </c>
+      <c r="C11" t="str" s="185">
+        <v>exterior_finish</v>
+      </c>
+      <c r="D11" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E11" t="str" s="186">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="184">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str" s="185">
+        <v>新設サッシのオプション</v>
+      </c>
+      <c r="C12" t="str" s="185">
+        <v>native_options</v>
+      </c>
+      <c r="D12" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E12" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="184">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str" s="185">
+        <v>追加部材・オプション</v>
+      </c>
+      <c r="C13" t="str" s="185">
+        <v>options</v>
+      </c>
+      <c r="D13" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E13" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="184">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str" s="185">
+        <v>選択した部材の仕様</v>
+      </c>
+      <c r="C14" t="str" s="185">
+        <v>part_detail</v>
+      </c>
+      <c r="D14" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E14" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="184">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str" s="185">
+        <v>現場採寸・取付条件</v>
+      </c>
+      <c r="C15" t="str" s="185">
+        <v>survey</v>
+      </c>
+      <c r="D15" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E15" t="str" s="186">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="184">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str" s="185">
+        <v>製品寸法</v>
+      </c>
+      <c r="C16" t="str" s="185">
+        <v>size</v>
+      </c>
+      <c r="D16" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E16" t="str" s="186">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="184"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="186"/>
+      <c r="F17"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="187"/>
+      <c r="B18" s="188"/>
+      <c r="C18" s="188"/>
+      <c r="D18" s="188"/>
+      <c r="E18" s="189"/>
+      <c r="F18"/>
+    </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+    </row>
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>

--- a/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C16" t="str" s="185"/>
       <c r="D16" t="str" s="185">
-        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false, "dataType": "MULTI_ENUM", "meaning": "アングルカバーと見切材の組合せを複数選択する。"}</v>
       </c>
       <c r="E16" t="str" s="186">
         <v>UI_PRESENTATION</v>

--- a/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
@@ -1265,7 +1265,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1285,7 +1285,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1303,7 +1303,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1323,7 +1323,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1343,7 +1343,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1363,7 +1363,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1383,7 +1383,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1401,7 +1401,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1413,13 +1413,13 @@
       </c>
       <c r="C11" t="str" s="185"/>
       <c r="D11" t="str" s="185">
-        <v>{"label": "建物構造", "group": "context", "internal": false}</v>
+        <v>{"label": "建物構造", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E11" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1437,7 +1437,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1455,7 +1455,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1473,7 +1473,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1491,7 +1491,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1509,7 +1509,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1529,7 +1529,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1541,13 +1541,13 @@
       </c>
       <c r="C18" t="str" s="185"/>
       <c r="D18" t="str" s="185">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E18" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1559,13 +1559,13 @@
       </c>
       <c r="C19" t="str" s="185"/>
       <c r="D19" t="str" s="185">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E19" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1577,13 +1577,13 @@
       </c>
       <c r="C20" t="str" s="185"/>
       <c r="D20" t="str" s="185">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E20" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -10092,10 +10092,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="str" s="185">
-        <v>設置・施工条件</v>
+        <v>窓種・基本仕様</v>
       </c>
       <c r="C5" t="str" s="185">
-        <v>context</v>
+        <v>opening</v>
       </c>
       <c r="D5" t="str" s="185">
         <v>選択・確認</v>
@@ -10110,16 +10110,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="str" s="185">
-        <v>窓種・基本仕様</v>
+        <v>室内側の仕上げ・アングルカバー</v>
       </c>
       <c r="C6" t="str" s="185">
-        <v>opening</v>
+        <v>interior_finish</v>
       </c>
       <c r="D6" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E6" t="str" s="186">
-        <v>対応する項目のみ表示</v>
+        <v>本体色に連動</v>
       </c>
       <c r="F6"/>
     </row>
@@ -10128,16 +10128,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="str" s="185">
-        <v>本体色</v>
+        <v>室外側の仕上げ・化粧カバー</v>
       </c>
       <c r="C7" t="str" s="185">
-        <v>finish</v>
+        <v>exterior_finish</v>
       </c>
       <c r="D7" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E7" t="str" s="186">
-        <v>対応する項目のみ表示</v>
+        <v>本体色に連動</v>
       </c>
       <c r="F7"/>
     </row>
@@ -10146,10 +10146,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="str" s="185">
-        <v>網戸</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C8" t="str" s="185">
-        <v>screen</v>
+        <v>options</v>
       </c>
       <c r="D8" t="str" s="185">
         <v>選択・確認</v>
@@ -10164,10 +10164,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="str" s="185">
-        <v>ガラス</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C9" t="str" s="185">
-        <v>glazing</v>
+        <v>part_detail</v>
       </c>
       <c r="D9" t="str" s="185">
         <v>選択・確認</v>
@@ -10182,125 +10182,65 @@
         <v>7</v>
       </c>
       <c r="B10" t="str" s="185">
-        <v>室内側の仕上げ・アングルカバー</v>
+        <v>現場採寸・取付条件</v>
       </c>
       <c r="C10" t="str" s="185">
-        <v>interior_finish</v>
+        <v>survey</v>
       </c>
       <c r="D10" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E10" t="str" s="186">
-        <v>本体色に連動</v>
+        <v>採寸後に再評価</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11">
-      <c r="A11" t="n" s="184">
-        <v>8</v>
-      </c>
-      <c r="B11" t="str" s="185">
-        <v>室外側の仕上げ・化粧カバー</v>
-      </c>
-      <c r="C11" t="str" s="185">
-        <v>exterior_finish</v>
-      </c>
-      <c r="D11" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E11" t="str" s="186">
-        <v>本体色に連動</v>
-      </c>
+      <c r="A11" s="184"/>
+      <c r="B11" s="185"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="185"/>
+      <c r="E11" s="186"/>
       <c r="F11"/>
     </row>
     <row r="12">
-      <c r="A12" t="n" s="184">
-        <v>9</v>
-      </c>
-      <c r="B12" t="str" s="185">
-        <v>新設サッシのオプション</v>
-      </c>
-      <c r="C12" t="str" s="185">
-        <v>native_options</v>
-      </c>
-      <c r="D12" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E12" t="str" s="186">
-        <v>対応する項目のみ表示</v>
-      </c>
+      <c r="A12" s="184"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="186"/>
       <c r="F12"/>
     </row>
     <row r="13">
-      <c r="A13" t="n" s="184">
-        <v>10</v>
-      </c>
-      <c r="B13" t="str" s="185">
-        <v>追加部材・オプション</v>
-      </c>
-      <c r="C13" t="str" s="185">
-        <v>options</v>
-      </c>
-      <c r="D13" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E13" t="str" s="186">
-        <v>対応する項目のみ表示</v>
-      </c>
+      <c r="A13" s="184"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="186"/>
       <c r="F13"/>
     </row>
     <row r="14">
-      <c r="A14" t="n" s="184">
-        <v>11</v>
-      </c>
-      <c r="B14" t="str" s="185">
-        <v>選択した部材の仕様</v>
-      </c>
-      <c r="C14" t="str" s="185">
-        <v>part_detail</v>
-      </c>
-      <c r="D14" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E14" t="str" s="186">
-        <v>対応する項目のみ表示</v>
-      </c>
+      <c r="A14" s="184"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="186"/>
       <c r="F14"/>
     </row>
     <row r="15">
-      <c r="A15" t="n" s="184">
-        <v>12</v>
-      </c>
-      <c r="B15" t="str" s="185">
-        <v>現場採寸・取付条件</v>
-      </c>
-      <c r="C15" t="str" s="185">
-        <v>survey</v>
-      </c>
-      <c r="D15" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E15" t="str" s="186">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A15" s="184"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
+      <c r="E15" s="186"/>
       <c r="F15"/>
     </row>
     <row r="16">
-      <c r="A16" t="n" s="184">
-        <v>13</v>
-      </c>
-      <c r="B16" t="str" s="185">
-        <v>製品寸法</v>
-      </c>
-      <c r="C16" t="str" s="185">
-        <v>size</v>
-      </c>
-      <c r="D16" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E16" t="str" s="186">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A16" s="184"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="186"/>
       <c r="F16"/>
     </row>
     <row r="17">

--- a/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
@@ -1250,7 +1250,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str" s="184">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B3" t="str" s="185">
         <v>exterior_cover_color</v>
@@ -1265,12 +1265,12 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str" s="184">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B4" t="str" s="185">
         <v>interior_cover_color</v>
@@ -1285,25 +1285,27 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str" s="184">
-        <v>フロー</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B5" t="str" s="185">
-        <v>referenced_series_id</v>
-      </c>
-      <c r="C5" t="str" s="185"/>
+        <v>attachment_frame_spec</v>
+      </c>
+      <c r="C5" t="str" s="185">
+        <v>installation_method</v>
+      </c>
       <c r="D5" t="str" s="185">
-        <v>{"label": "新設サッシシリーズ", "group": "opening", "internal": false}</v>
+        <v>{"targetField": "attachment_frame_spec", "parents": ["installation_method"], "cases": [{"when": {"installation_method": "STANDARD"}, "value": "ATT-TW-FRAME-STD"}, {"when": {"installation_method": "INNER_FIT_INSET"}, "value": "ATT-TW-FRAME-INNER-SINGLE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "ATT-TW-FRAME-INNER-SINGLE"}], "resolvedMessage": "施工仕様に連動しています。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "アタッチ枠の対応を確認してください。"}</v>
       </c>
       <c r="E5" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1311,19 +1313,17 @@
         <v>フロー</v>
       </c>
       <c r="B6" t="str" s="185">
-        <v>referenced_window_id</v>
-      </c>
-      <c r="C6" t="str" s="185">
         <v>referenced_series_id</v>
       </c>
+      <c r="C6" t="str" s="185"/>
       <c r="D6" t="str" s="185">
-        <v>{"label": "新設サッシ窓種", "group": "opening", "internal": false}</v>
+        <v>{"label": "新設サッシシリーズ", "group": "opening", "internal": false}</v>
       </c>
       <c r="E6" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1331,19 +1331,19 @@
         <v>フロー</v>
       </c>
       <c r="B7" t="str" s="185">
-        <v>exterior_cover_color</v>
+        <v>referenced_window_id</v>
       </c>
       <c r="C7" t="str" s="185">
-        <v>new_sash_exterior_color</v>
+        <v>referenced_series_id</v>
       </c>
       <c r="D7" t="str" s="185">
-        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "新設サッシ窓種", "group": "opening", "internal": false}</v>
       </c>
       <c r="E7" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1351,19 +1351,19 @@
         <v>フロー</v>
       </c>
       <c r="B8" t="str" s="185">
-        <v>interior_cover_color</v>
+        <v>exterior_cover_color</v>
       </c>
       <c r="C8" t="str" s="185">
-        <v>new_sash_interior_color</v>
+        <v>new_sash_exterior_color</v>
       </c>
       <c r="D8" t="str" s="185">
-        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
       </c>
       <c r="E8" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1371,19 +1371,19 @@
         <v>フロー</v>
       </c>
       <c r="B9" t="str" s="185">
-        <v>wooden_casing_color</v>
+        <v>interior_cover_color</v>
       </c>
       <c r="C9" t="str" s="185">
-        <v>options</v>
+        <v>new_sash_interior_color</v>
       </c>
       <c r="D9" t="str" s="185">
-        <v>{"label": "木製ケーシング色", "group": "part_detail", "internal": false}</v>
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
       </c>
       <c r="E9" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1391,17 +1391,19 @@
         <v>フロー</v>
       </c>
       <c r="B10" t="str" s="185">
+        <v>wooden_casing_color</v>
+      </c>
+      <c r="C10" t="str" s="185">
         <v>options</v>
       </c>
-      <c r="C10" t="str" s="185"/>
       <c r="D10" t="str" s="185">
-        <v>{"label": "追加部材・オプション", "group": "options", "internal": false}</v>
+        <v>{"label": "木製ケーシング色", "group": "part_detail", "internal": false}</v>
       </c>
       <c r="E10" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1409,17 +1411,17 @@
         <v>フロー</v>
       </c>
       <c r="B11" t="str" s="185">
-        <v>building_structure</v>
+        <v>options</v>
       </c>
       <c r="C11" t="str" s="185"/>
       <c r="D11" t="str" s="185">
-        <v>{"label": "建物構造", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "追加部材・オプション", "group": "options", "internal": false}</v>
       </c>
       <c r="E11" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1437,7 +1439,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1455,7 +1457,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1473,7 +1475,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1491,7 +1493,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1503,13 +1505,13 @@
       </c>
       <c r="C16" t="str" s="185"/>
       <c r="D16" t="str" s="185">
-        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false, "dataType": "MULTI_ENUM", "meaning": "アングルカバーと見切材の組合せを複数選択する。"}</v>
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
       </c>
       <c r="E16" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1529,7 +1531,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1537,17 +1539,19 @@
         <v>フロー</v>
       </c>
       <c r="B18" t="str" s="185">
-        <v>survey_cover_top</v>
-      </c>
-      <c r="C18" t="str" s="185"/>
+        <v>installation_method</v>
+      </c>
+      <c r="C18" t="str" s="185">
+        <v>referenced_window_id</v>
+      </c>
       <c r="D18" t="str" s="185">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "内はめ仕様", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E18" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1555,17 +1559,19 @@
         <v>フロー</v>
       </c>
       <c r="B19" t="str" s="185">
-        <v>survey_cover_bottom</v>
-      </c>
-      <c r="C19" t="str" s="185"/>
+        <v>attachment_frame_spec</v>
+      </c>
+      <c r="C19" t="str" s="185">
+        <v>installation_method</v>
+      </c>
       <c r="D19" t="str" s="185">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "アタッチ枠仕様", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E19" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1573,17 +1579,39 @@
         <v>フロー</v>
       </c>
       <c r="B20" t="str" s="185">
-        <v>survey_cover_side</v>
-      </c>
-      <c r="C20" t="str" s="185"/>
+        <v>attachment_finished_w</v>
+      </c>
+      <c r="C20" t="str" s="185">
+        <v>survey_w</v>
+      </c>
       <c r="D20" t="str" s="185">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "アタッチ枠仕上がり幅 WD（mm）", "group": "size", "internal": false}</v>
       </c>
       <c r="E20" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B21" t="str">
+        <v>attachment_finished_h</v>
+      </c>
+      <c r="C21" t="str">
+        <v>survey_h</v>
+      </c>
+      <c r="D21" t="str">
+        <v>{"label": "アタッチ枠仕上がり高さ HD（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E21" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F21" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -1607,7 +1635,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="178" t="str">
+      <c r="A1" t="str" s="178">
         <v>90_Evidence｜アタッチ枠TW 根拠管理</v>
       </c>
       <c r="B1" s="178"/>
@@ -1620,7 +1648,7 @@
       <c r="I1" s="178"/>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="179" t="str">
+      <c r="A2" t="str" s="179">
         <v>リプラス公式資料とTW正本を分離して記録。TW本体仕様はTW正本、アタッチ枠固有差分はリプラス資料を根拠とする。</v>
       </c>
       <c r="B2" s="179"/>
@@ -1632,715 +1660,654 @@
       <c r="H2" s="179"/>
       <c r="I2" s="179"/>
     </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="181" t="str">
+      <c r="A4" t="str" s="181">
         <v>evidence_id</v>
       </c>
-      <c r="B4" s="182" t="str">
+      <c r="B4" t="str" s="182">
         <v>情報源種別</v>
       </c>
-      <c r="C4" s="182" t="str">
+      <c r="C4" t="str" s="182">
         <v>資料名</v>
       </c>
-      <c r="D4" s="182" t="str">
+      <c r="D4" t="str" s="182">
         <v>発行年月</v>
       </c>
-      <c r="E4" s="182" t="str">
+      <c r="E4" t="str" s="182">
         <v>ページ/箇所</v>
       </c>
-      <c r="F4" s="182" t="str">
+      <c r="F4" t="str" s="182">
         <v>URL</v>
       </c>
-      <c r="G4" s="182" t="str">
+      <c r="G4" t="str" s="182">
         <v>確認日</v>
       </c>
-      <c r="H4" s="182" t="str">
+      <c r="H4" t="str" s="182">
         <v>確度</v>
       </c>
-      <c r="I4" s="183" t="str">
+      <c r="I4" t="str" s="183">
         <v>根拠内容</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="184" t="str">
+      <c r="A5" t="str" s="184">
         <v>ATT-TW-EV-001</v>
       </c>
-      <c r="B5" s="185" t="str">
+      <c r="B5" t="str" s="185">
         <v>共通仕様</v>
       </c>
-      <c r="C5" s="185" t="str">
+      <c r="C5" t="str" s="185">
         <v>サッシ商品マスター共通仕様書_v0.1</v>
       </c>
-      <c r="D5" s="185" t="str">
+      <c r="D5" t="str" s="185">
         <v>2026-08-30更新</v>
       </c>
-      <c r="E5" s="185" t="str">
+      <c r="E5" t="str" s="185">
         <v>§5,9,23-34</v>
       </c>
-      <c r="F5" s="185" t="str">
+      <c r="F5" t="str" s="185">
         <v>https://docs.google.com/document/d/1MfixkbV1cZ__DtBknEKsix_nnrXQqjc-LZtXUHwJv_A/edit</v>
       </c>
-      <c r="G5" s="185" t="str">
+      <c r="G5" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H5" s="185" t="str">
+      <c r="H5" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I5" s="186" t="str">
+      <c r="I5" t="str" s="186">
         <v>防火別体系、Evidence、UI非表示、耐風圧特殊案件、OP依存</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="184" t="str">
+      <c r="A6" t="str" s="184">
         <v>ATT-TW-EV-002</v>
       </c>
-      <c r="B6" s="185" t="str">
+      <c r="B6" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C6" s="185" t="str">
+      <c r="C6" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D6" s="185" t="str">
+      <c r="D6" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E6" s="185" t="str">
+      <c r="E6" t="str" s="185">
         <v>p.35</v>
       </c>
-      <c r="F6" s="185" t="str">
+      <c r="F6" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G6" s="185" t="str">
+      <c r="G6" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H6" s="185" t="str">
+      <c r="H6" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I6" s="186" t="str">
+      <c r="I6" t="str" s="186">
         <v>アタッチ枠TW商品構造、対応シリーズ、釘打ちフィンカット、色、浴室不可</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="184" t="str">
+      <c r="A7" t="str" s="184">
         <v>ATT-TW-EV-003</v>
       </c>
-      <c r="B7" s="185" t="str">
+      <c r="B7" t="str" s="185">
         <v>TW正本</v>
       </c>
-      <c r="C7" s="185" t="str">
+      <c r="C7" t="str" s="185">
         <v>サッシ商品マスター_v0.1</v>
       </c>
-      <c r="D7" s="185" t="str">
+      <c r="D7" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E7" s="185" t="str">
+      <c r="E7" t="str" s="185">
         <v>02_シリーズ / 03A_シリーズ窓種設定</v>
       </c>
-      <c r="F7" s="185" t="str">
+      <c r="F7" t="str" s="185">
         <v>https://docs.google.com/spreadsheets/d/1ordbcPQS7XhptLMjRON2oxmdsPhs-aY-Wm7quPHvM9U/edit</v>
       </c>
-      <c r="G7" s="185" t="str">
+      <c r="G7" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H7" s="185" t="str">
+      <c r="H7" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I7" s="186" t="str">
+      <c r="I7" t="str" s="186">
         <v>SER-LIX-TW、正式SWT ID。TW本体Single Source of Truth</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="184" t="str">
+      <c r="A8" t="str" s="184">
         <v>ATT-TW-EV-004</v>
       </c>
-      <c r="B8" s="185" t="str">
+      <c r="B8" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C8" s="185" t="str">
+      <c r="C8" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D8" s="185" t="str">
+      <c r="D8" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E8" s="185" t="str">
+      <c r="E8" t="str" s="185">
         <v>p.203</v>
       </c>
-      <c r="F8" s="185" t="str">
+      <c r="F8" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G8" s="185" t="str">
+      <c r="G8" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H8" s="185" t="str">
+      <c r="H8" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I8" s="186" t="str">
+      <c r="I8" t="str" s="186">
         <v>アタッチ枠TW新設サッシ/TW別手配の対応品種可否、連結ねじ注記</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="184" t="str">
+      <c r="A9" t="str" s="184">
         <v>ATT-TW-EV-005</v>
       </c>
-      <c r="B9" s="185" t="str">
+      <c r="B9" t="str" s="185">
         <v>TW正本</v>
       </c>
-      <c r="C9" s="185" t="str">
+      <c r="C9" t="str" s="185">
         <v>サッシ商品マスター_v0.1</v>
       </c>
-      <c r="D9" s="185" t="str">
+      <c r="D9" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E9" s="185" t="str">
+      <c r="E9" t="str" s="185">
         <v>03A_シリーズ窓種設定</v>
       </c>
-      <c r="F9" s="185" t="str">
+      <c r="F9" t="str" s="185">
         <v>https://docs.google.com/spreadsheets/d/1ordbcPQS7XhptLMjRON2oxmdsPhs-aY-Wm7quPHvM9U/edit</v>
       </c>
-      <c r="G9" s="185" t="str">
+      <c r="G9" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H9" s="185" t="str">
+      <c r="H9" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I9" s="186" t="str">
+      <c r="I9" t="str" s="186">
         <v>グレモンT/TF/TFT、OP、横、High、上げ下げ、FIX分割IDの正本確認</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="184" t="str">
+      <c r="A10" t="str" s="184">
         <v>ATT-TW-EV-006</v>
       </c>
-      <c r="B10" s="185" t="str">
+      <c r="B10" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C10" s="185" t="str">
+      <c r="C10" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D10" s="185" t="str">
+      <c r="D10" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E10" s="185" t="str">
+      <c r="E10" t="str" s="185">
         <v>p.188 基本寸法/納まり参考図</v>
       </c>
-      <c r="F10" s="185" t="str">
+      <c r="F10" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G10" s="185" t="str">
+      <c r="G10" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H10" s="185" t="str">
+      <c r="H10" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I10" s="186" t="str">
+      <c r="I10" t="str" s="186">
         <v>WD=WS-10、HD=HS-10、TW_W=WS-38、TW_H=HS-50</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="184" t="str">
+      <c r="A11" t="str" s="184">
         <v>ATT-TW-EV-007</v>
       </c>
-      <c r="B11" s="185" t="str">
+      <c r="B11" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C11" s="185" t="str">
+      <c r="C11" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D11" s="185" t="str">
+      <c r="D11" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E11" s="185" t="str">
+      <c r="E11" t="str" s="185">
         <v>p.196,200</v>
       </c>
-      <c r="F11" s="185" t="str">
+      <c r="F11" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G11" s="185" t="str">
+      <c r="G11" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H11" s="185" t="str">
+      <c r="H11" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I11" s="186" t="str">
+      <c r="I11" t="str" s="186">
         <v>構造/防火/既設材質、既設窓対応表、雨戸/シャッターのアタッチ枠不可</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="184" t="str">
+      <c r="A12" t="str" s="184">
         <v>ATT-TW-EV-008</v>
       </c>
-      <c r="B12" s="185" t="str">
+      <c r="B12" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C12" s="185" t="str">
+      <c r="C12" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D12" s="185" t="str">
+      <c r="D12" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E12" s="185" t="str">
+      <c r="E12" t="str" s="185">
         <v>p.201</v>
       </c>
-      <c r="F12" s="185" t="str">
+      <c r="F12" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G12" s="185" t="str">
+      <c r="G12" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H12" s="185" t="str">
+      <c r="H12" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I12" s="186" t="str">
+      <c r="I12" t="str" s="186">
         <v>アタッチ枠TW 既設枠見込み100mm以下</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="184" t="str">
+      <c r="A13" t="str" s="184">
         <v>ATT-TW-EV-009</v>
       </c>
-      <c r="B13" s="185" t="str">
+      <c r="B13" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C13" s="185" t="str">
+      <c r="C13" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D13" s="185" t="str">
+      <c r="D13" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E13" s="185" t="str">
+      <c r="E13" t="str" s="185">
         <v>p.208-210</v>
       </c>
-      <c r="F13" s="185" t="str">
+      <c r="F13" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G13" s="185" t="str">
+      <c r="G13" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H13" s="185" t="str">
+      <c r="H13" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I13" s="186" t="str">
+      <c r="I13" t="str" s="186">
         <v>3点採寸、変形/たおれ、既設枠測定、二重サッシ採寸</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="184" t="str">
+      <c r="A14" t="str" s="184">
         <v>ATT-TW-EV-010</v>
       </c>
-      <c r="B14" s="185" t="str">
+      <c r="B14" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C14" s="185" t="str">
+      <c r="C14" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D14" s="185" t="str">
+      <c r="D14" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E14" s="185" t="str">
+      <c r="E14" t="str" s="185">
         <v>p.209</v>
       </c>
-      <c r="F14" s="185" t="str">
+      <c r="F14" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G14" s="185" t="str">
+      <c r="G14" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H14" s="185" t="str">
+      <c r="H14" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I14" s="186" t="str">
+      <c r="I14" t="str" s="186">
         <v>下枠補強金具29～48mmとスペーサー補正</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="184" t="str">
+      <c r="A15" t="str" s="184">
         <v>ATT-TW-EV-011</v>
       </c>
-      <c r="B15" s="185" t="str">
+      <c r="B15" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C15" s="185" t="str">
+      <c r="C15" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D15" s="185" t="str">
+      <c r="D15" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E15" s="185" t="str">
+      <c r="E15" t="str" s="185">
         <v>p.211</v>
       </c>
-      <c r="F15" s="185" t="str">
+      <c r="F15" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G15" s="185" t="str">
+      <c r="G15" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H15" s="185" t="str">
+      <c r="H15" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I15" s="186" t="str">
+      <c r="I15" t="str" s="186">
         <v>アタッチ枠TW 化粧カバー見付 大/中/小：上71.5/36.5/16.5、下91/56/36、縦34/34/9</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="184" t="str">
+      <c r="A16" t="str" s="184">
         <v>ATT-TW-EV-012</v>
       </c>
-      <c r="B16" s="185" t="str">
+      <c r="B16" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C16" s="185" t="str">
+      <c r="C16" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E16" s="185" t="str">
+      <c r="E16" t="str" s="185">
         <v>p.262</v>
       </c>
-      <c r="F16" s="185" t="str">
+      <c r="F16" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G16" s="185" t="str">
+      <c r="G16" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H16" s="185" t="str">
+      <c r="H16" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I16" s="186" t="str">
+      <c r="I16" t="str" s="186">
         <v>アタッチ枠装飾窓：標準 / 既設単体 内嵌め用の部材詳細</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="184" t="str">
+      <c r="A17" t="str" s="184">
         <v>ATT-TW-EV-013</v>
       </c>
-      <c r="B17" s="185" t="str">
+      <c r="B17" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C17" s="185" t="str">
+      <c r="C17" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D17" s="185" t="str">
+      <c r="D17" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E17" s="185" t="str">
+      <c r="E17" t="str" s="185">
         <v>p.72 有償品対応一覧</v>
       </c>
-      <c r="F17" s="185" t="str">
+      <c r="F17" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G17" s="185" t="str">
+      <c r="G17" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H17" s="185" t="str">
+      <c r="H17" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I17" s="186" t="str">
+      <c r="I17" t="str" s="186">
         <v>小開口アーム、固定/可動網戸溝カバー、後付ビード、連窓方立、段窓無目の設定</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="184" t="str">
+      <c r="A18" t="str" s="184">
         <v>ATT-TW-EV-014</v>
       </c>
-      <c r="B18" s="185" t="str">
+      <c r="B18" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C18" s="185" t="str">
+      <c r="C18" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ</v>
       </c>
-      <c r="D18" s="185" t="str">
+      <c r="D18" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E18" s="185" t="str">
+      <c r="E18" t="str" s="185">
         <v>p.73,188,263</v>
       </c>
-      <c r="F18" s="185" t="str">
+      <c r="F18" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G18" s="185" t="str">
+      <c r="G18" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H18" s="185" t="str">
+      <c r="H18" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I18" s="186" t="str">
+      <c r="I18" t="str" s="186">
         <v>気密テープ、調整スペーサー、アングルカバー、見切材、連結ねじ等施工部材</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="187" t="str">
+      <c r="A19" t="str" s="187">
         <v>ATT-TW-EV-015</v>
       </c>
-      <c r="B19" s="188" t="str">
+      <c r="B19" t="str" s="188">
         <v>公式資料横断</v>
       </c>
-      <c r="C19" s="188" t="str">
+      <c r="C19" t="str" s="188">
         <v>リプラス/TW公式資料</v>
       </c>
-      <c r="D19" s="188" t="str">
+      <c r="D19" t="str" s="188">
         <v>現行</v>
       </c>
-      <c r="E19" s="188" t="str">
+      <c r="E19" t="str" s="188">
         <v>特殊寸法・ガラス/耐風圧/連段</v>
       </c>
-      <c r="F19" s="188" t="str">
+      <c r="F19" t="str" s="188">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G19" s="188" t="str">
+      <c r="G19" t="str" s="188">
         <v>2026-08-31</v>
       </c>
-      <c r="H19" s="188" t="str">
+      <c r="H19" t="str" s="188">
         <v>HIGH</v>
       </c>
-      <c r="I19" s="189" t="str">
+      <c r="I19" t="str" s="189">
         <v>通常見積外の特殊案件は公式表/見積システム最終確認</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>DELTA-SPACER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>PDF 52,104,116,120</t>
-        </is>
-      </c>
-      <c r="F20" s="39" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G20" s="39" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H20" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I20" s="40" t="inlineStr">
-        <is>
-          <t>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A20" t="str" s="38">
+        <v>DELTA-SPACER-EV-V4</v>
+      </c>
+      <c r="B20" t="str" s="39">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C20" t="str" s="39">
+        <v>IS9800</v>
+      </c>
+      <c r="D20" t="str" s="39">
+        <v>2026-10</v>
+      </c>
+      <c r="E20" t="str" s="39">
+        <v>PDF 52,104,116,120</v>
+      </c>
+      <c r="F20" t="str" s="39">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G20" t="str" s="39">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H20" t="str" s="39">
+        <v>HIGH</v>
+      </c>
+      <c r="I20" t="str" s="40">
+        <v>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-CASING-EV-V4</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>PDF 51,115,119</t>
-        </is>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I21" s="28" t="inlineStr">
-        <is>
-          <t>UPDATE_WOODEN_CASING_COLOR_SCOPE / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A21" t="str" s="28">
+        <v>DELTA-CASING-EV-V4</v>
+      </c>
+      <c r="B21" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C21" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D21" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E21" t="str" s="28">
+        <v>PDF 51,115,119</v>
+      </c>
+      <c r="F21" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G21" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H21" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I21" t="str" s="28">
+        <v>UPDATE_WOODEN_CASING_COLOR_SCOPE / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-FILLER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
-        <is>
-          <t>PDF 51,115,119</t>
-        </is>
-      </c>
-      <c r="F22" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I22" s="28" t="inlineStr">
-        <is>
-          <t>UPDATE_FILLER_NAME_AND_VARIANTS / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A22" t="str" s="28">
+        <v>DELTA-FILLER-EV-V4</v>
+      </c>
+      <c r="B22" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C22" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D22" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E22" t="str" s="28">
+        <v>PDF 51,115,119</v>
+      </c>
+      <c r="F22" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G22" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H22" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I22" t="str" s="28">
+        <v>UPDATE_FILLER_NAME_AND_VARIANTS / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-LEADTIME-EV-V4</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="inlineStr">
-        <is>
-          <t>PDF 235</t>
-        </is>
-      </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I23" s="28" t="inlineStr">
-        <is>
-          <t>SOURCE_NOTE_ONLY / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A23" t="str" s="28">
+        <v>DELTA-LEADTIME-EV-V4</v>
+      </c>
+      <c r="B23" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C23" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D23" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E23" t="str" s="28">
+        <v>PDF 235</v>
+      </c>
+      <c r="F23" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G23" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H23" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I23" t="str" s="28">
+        <v>SOURCE_NOTE_ONLY / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>REF-TW-CURRENT-20261009-V4</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>Current正本参照</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>integrated-v0.5 Current Authoring</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>固定参照ID/SHA</t>
-        </is>
-      </c>
-      <c r="F24" s="28" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/10-ygy_wcdXN2u9brqU1AhucboJv5N5qk/view</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I24" s="28" t="inlineStr">
-        <is>
-          <t>5062503d3387999c2eed0862b3386e5248ae131008cbc37975956d709d598ba6</t>
-        </is>
+      <c r="A24" t="str" s="28">
+        <v>REF-TW-CURRENT-20261009-V4</v>
+      </c>
+      <c r="B24" t="str" s="28">
+        <v>Current正本参照</v>
+      </c>
+      <c r="C24" t="str" s="28">
+        <v>integrated-v0.5 Current Authoring</v>
+      </c>
+      <c r="D24" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="E24" t="str" s="28">
+        <v>固定参照ID/SHA</v>
+      </c>
+      <c r="F24" t="str" s="28">
+        <v>https://drive.google.com/file/d/10-ygy_wcdXN2u9brqU1AhucboJv5N5qk/view</v>
+      </c>
+      <c r="G24" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H24" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I24" t="str" s="28">
+        <v>5062503d3387999c2eed0862b3386e5248ae131008cbc37975956d709d598ba6</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
+      <c r="A25" t="str" s="28">
+        <v>EV-DIMENSIONS-INNER-FIT-V11</v>
+      </c>
+      <c r="B25" t="str" s="28">
+        <v>公式商品カタログ</v>
+      </c>
+      <c r="C25" t="str" s="28">
+        <v>リプラス SN1200</v>
+      </c>
+      <c r="D25" t="str" s="28">
+        <v>2025-08</v>
+      </c>
+      <c r="E25" t="str" s="28">
+        <v>PDF252/254・231/233/247/249/251</v>
+      </c>
+      <c r="F25" t="str" s="28">
+        <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
+      </c>
+      <c r="G25" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H25" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I25" t="str" s="28">
+        <v>採寸/出来寸の相互換算と標準/内はめの施工仕様を共通Runtimeへ接続</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="28"/>
@@ -10083,7 +10050,7 @@
         <v>リプラス住宅用 → 仕様</v>
       </c>
       <c r="E4" t="str" s="186">
-        <v>今回承認されたアプリ運用ルール</v>
+        <v>アプリ運用ルール</v>
       </c>
       <c r="F4"/>
     </row>
@@ -10110,16 +10077,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="str" s="185">
-        <v>室内側の仕上げ・アングルカバー</v>
+        <v>内はめ仕様</v>
       </c>
       <c r="C6" t="str" s="185">
-        <v>interior_finish</v>
+        <v>inner_fit</v>
       </c>
       <c r="D6" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E6" t="str" s="186">
-        <v>本体色に連動</v>
+        <v>ガラスの後で選択</v>
       </c>
       <c r="F6"/>
     </row>
@@ -10128,16 +10095,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="str" s="185">
-        <v>室外側の仕上げ・化粧カバー</v>
+        <v>室内側の仕上げ・アングルカバー</v>
       </c>
       <c r="C7" t="str" s="185">
-        <v>exterior_finish</v>
+        <v>interior_finish</v>
       </c>
       <c r="D7" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E7" t="str" s="186">
-        <v>本体色に連動</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F7"/>
     </row>
@@ -10146,10 +10113,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="str" s="185">
-        <v>追加部材・オプション</v>
+        <v>室外側の仕上げ・化粧カバー</v>
       </c>
       <c r="C8" t="str" s="185">
-        <v>options</v>
+        <v>exterior_finish</v>
       </c>
       <c r="D8" t="str" s="185">
         <v>選択・確認</v>
@@ -10164,10 +10131,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="str" s="185">
-        <v>選択した部材の仕様</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C9" t="str" s="185">
-        <v>part_detail</v>
+        <v>options</v>
       </c>
       <c r="D9" t="str" s="185">
         <v>選択・確認</v>
@@ -10182,33 +10149,53 @@
         <v>7</v>
       </c>
       <c r="B10" t="str" s="185">
-        <v>現場採寸・取付条件</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C10" t="str" s="185">
-        <v>survey</v>
+        <v>part_detail</v>
       </c>
       <c r="D10" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E10" t="str" s="186">
-        <v>採寸後に再評価</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11">
-      <c r="A11" s="184"/>
-      <c r="B11" s="185"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="186"/>
+      <c r="A11" t="n" s="184">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str" s="185">
+        <v>現場採寸・取付条件</v>
+      </c>
+      <c r="C11" t="str" s="185">
+        <v>survey</v>
+      </c>
+      <c r="D11" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E11" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12">
-      <c r="A12" s="184"/>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="186"/>
+      <c r="A12" t="n" s="184">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str" s="185">
+        <v>製品寸法</v>
+      </c>
+      <c r="C12" t="str" s="185">
+        <v>size</v>
+      </c>
+      <c r="D12" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E12" t="str" s="186">
+        <v>採寸と仕上がりを併記</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13">

--- a/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ATT_TW.xlsx
@@ -1265,7 +1265,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1285,7 +1285,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1305,7 +1305,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1323,7 +1323,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1343,7 +1343,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1357,13 +1357,13 @@
         <v>new_sash_exterior_color</v>
       </c>
       <c r="D8" t="str" s="185">
-        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E8" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1377,13 +1377,13 @@
         <v>new_sash_interior_color</v>
       </c>
       <c r="D9" t="str" s="185">
-        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E9" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1403,7 +1403,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1421,7 +1421,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1439,7 +1439,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1457,7 +1457,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1475,7 +1475,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1493,7 +1493,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1511,7 +1511,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1531,7 +1531,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1551,7 +1551,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1571,7 +1571,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1591,7 +1591,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1611,7 +1611,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
   </sheetData>
